--- a/data/S2016_17_FINAL.xlsx
+++ b/data/S2016_17_FINAL.xlsx
@@ -1,36 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_liga" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20_1liga" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="30_2liga" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KVAL" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="30PRAH" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="30STRC" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="30JHCK" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="30PLZN" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="30KVRY" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="30USTE" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="30LIBE" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="30HRAD" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="30PARD" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="30VYSO" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="30JHMR" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="30SVMR" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NOTES" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NOTES1" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SYSTEM" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SERIES" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CLUBS" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="META" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="10_liga" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="20_1liga" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="30_2liga" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="KVAL" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="30PRAH" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="30STRC" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="30JHCK" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="30PLZN" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="30KVRY" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="30USTE" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="30LIBE" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="30HRAD" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="30PARD" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="30VYSO" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="30JHMR" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="30SVMR" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="NOTES" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="NOTES1" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="SYSTEM" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="SERIES" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="CLUBS" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="META" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="TODO" sheetId="23" state="visible" r:id="rId23"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">'TODO'!$A$1:$F$2</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -38,7 +41,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -53,8 +56,12 @@
       <name val="Arial"/>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -71,6 +78,11 @@
         <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00305496"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -84,11 +96,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -14568,7 +14586,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14617,6 +14635,23 @@
       <c r="D2" t="inlineStr">
         <is>
           <t>H</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0031</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL L35'</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
         </is>
       </c>
     </row>
@@ -14689,7 +14724,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K229"/>
+  <dimension ref="A1:L229"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14748,6 +14783,11 @@
           <t>note</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>prev_node_id</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -14785,6 +14825,11 @@
           <t>14 týmů (4-col): základ + předkolo/QF/SF/finále + Play Out + baráž. Mistr: HC Kometa Brno.</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0001</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -14822,6 +14867,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0002</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -14859,6 +14909,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0003</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -14896,6 +14951,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0004</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -14933,6 +14993,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0005</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -14970,6 +15035,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0006</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -15007,6 +15077,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0007</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -15044,6 +15119,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0008</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -15081,6 +15161,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0009</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -15118,6 +15203,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0010</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -15155,6 +15245,11 @@
           <t>1.liga: základ + QF/SF + Play out + baráž.</t>
         </is>
       </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0011</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -15192,6 +15287,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0012</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -15229,6 +15329,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0013</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -15266,6 +15371,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0014</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -15303,6 +15413,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0015</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -15340,6 +15455,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0016</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -15377,6 +15497,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0017</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -15414,6 +15539,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0018</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -15451,6 +15581,11 @@
           <t>II.liga: skupiny + QF/SF/finále + baráž o 2.ligu.</t>
         </is>
       </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0019</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -15488,6 +15623,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0020</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -15525,6 +15665,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0021</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -15562,6 +15707,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0022</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -15599,6 +15749,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0023</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -15636,6 +15791,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0024</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -15673,6 +15833,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0025</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -15710,6 +15875,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0026</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -15747,6 +15917,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0027</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -15784,6 +15959,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0028</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -15821,6 +16001,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0029</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -15858,6 +16043,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0030</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -15890,6 +16080,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0031</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -15927,6 +16122,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0032</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -15964,6 +16164,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0033</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -16001,6 +16206,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0034</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -16038,6 +16248,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0035</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -16107,6 +16322,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0039</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -16144,6 +16364,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0040</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -16218,6 +16443,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0169</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -16287,6 +16517,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0051</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -17022,6 +17257,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0065</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -17498,6 +17738,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0078</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -17609,6 +17854,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0169</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -18492,6 +18742,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0114</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -19227,6 +19482,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0126</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -19518,6 +19778,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0136</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -20105,6 +20370,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0149</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -20586,6 +20856,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0162</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -20697,6 +20972,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0165</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -20803,6 +21083,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0166</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -21025,6 +21310,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0170</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -21908,6 +22198,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0196</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -22199,6 +22494,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0207</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -22673,6 +22973,11 @@
       <c r="J217" t="inlineStr">
         <is>
           <t>complete</t>
+        </is>
+      </c>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>NODE_S2015_16_0220</t>
         </is>
       </c>
     </row>
@@ -42449,6 +42754,81 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="88" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>typ</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>popis</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>vyřešeno? (ANO/ne)</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>poznámka kolegy</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>pyramida (feeds_into)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0031</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>top-level kvalifikace bez feeds_into: 'KVAL L35'</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F2"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/data/S2016_17_FINAL.xlsx
+++ b/data/S2016_17_FINAL.xlsx
@@ -14724,7 +14724,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L229"/>
+  <dimension ref="A1:N229"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14786,6 +14786,16 @@
       <c r="L1" t="inlineStr">
         <is>
           <t>prev_node_id</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>entry</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>phase_order</t>
         </is>
       </c>
     </row>

--- a/data/S2016_17_FINAL.xlsx
+++ b/data/S2016_17_FINAL.xlsx
@@ -14872,6 +14872,16 @@
           <t>NODE_S2016_17_0001</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0004</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0009</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>complete</t>
@@ -14881,6 +14891,14 @@
         <is>
           <t>NODE_S2015_16_0002</t>
         </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>14 týmů</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -14956,6 +14974,16 @@
           <t>NODE_S2016_17_0003</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0005</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0009</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>complete</t>
@@ -14965,6 +14993,14 @@
         <is>
           <t>NODE_S2015_16_0004</t>
         </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>střed tabulky ZČ</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -14998,6 +15034,12 @@
           <t>NODE_S2016_17_0003</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0006</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>complete</t>
@@ -15007,6 +15049,14 @@
         <is>
           <t>NODE_S2015_16_0005</t>
         </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>horní ZČ + postupující z předkola</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -15040,6 +15090,16 @@
           <t>NODE_S2016_17_0003</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0008</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0007</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
           <t>complete</t>
@@ -15049,6 +15109,14 @@
         <is>
           <t>NODE_S2015_16_0006</t>
         </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -15082,6 +15150,8 @@
           <t>NODE_S2016_17_0003</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>complete</t>
@@ -15091,6 +15161,14 @@
         <is>
           <t>NODE_S2015_16_0007</t>
         </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>poražení SF</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -15124,6 +15202,8 @@
           <t>NODE_S2016_17_0003</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>complete</t>
@@ -15133,6 +15213,14 @@
         <is>
           <t>NODE_S2015_16_0008</t>
         </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="10">
@@ -15166,6 +15254,8 @@
           <t>NODE_S2016_17_0001</t>
         </is>
       </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>complete</t>
@@ -15175,6 +15265,14 @@
         <is>
           <t>NODE_S2015_16_0009</t>
         </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -15292,6 +15390,16 @@
           <t>NODE_S2016_17_0011</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0013</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0017</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
           <t>complete</t>
@@ -15301,6 +15409,14 @@
         <is>
           <t>NODE_S2015_16_0012</t>
         </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>14 týmů</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -15334,6 +15450,16 @@
           <t>NODE_S2016_17_0011</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0014</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0017</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr">
         <is>
           <t>complete</t>
@@ -15343,6 +15469,14 @@
         <is>
           <t>NODE_S2015_16_0013</t>
         </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>střed tabulky ZČ</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -15376,6 +15510,12 @@
           <t>NODE_S2016_17_0011</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0015</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>complete</t>
@@ -15385,6 +15525,14 @@
         <is>
           <t>NODE_S2015_16_0014</t>
         </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>horní ZČ + postupující z předkola</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -15418,6 +15566,12 @@
           <t>NODE_S2016_17_0011</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0016</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>complete</t>
@@ -15427,6 +15581,14 @@
         <is>
           <t>NODE_S2015_16_0015</t>
         </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="17">
@@ -15460,6 +15622,8 @@
           <t>NODE_S2016_17_0011</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>complete</t>
@@ -15469,6 +15633,14 @@
         <is>
           <t>NODE_S2015_16_0016</t>
         </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N17" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="18">
@@ -15502,6 +15674,8 @@
           <t>NODE_S2016_17_0011</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
           <t>complete</t>
@@ -15511,6 +15685,14 @@
         <is>
           <t>NODE_S2015_16_0017</t>
         </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -15796,6 +15978,12 @@
           <t>NODE_S2016_17_0019</t>
         </is>
       </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0025</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
           <t>complete</t>
@@ -15805,6 +15993,14 @@
         <is>
           <t>NODE_S2015_16_0024</t>
         </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>horní část ZČ</t>
+        </is>
+      </c>
+      <c r="N25" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -15838,6 +16034,12 @@
           <t>NODE_S2016_17_0019</t>
         </is>
       </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0026</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
           <t>complete</t>
@@ -15847,6 +16049,14 @@
         <is>
           <t>NODE_S2015_16_0025</t>
         </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>horní polovina ZČ</t>
+        </is>
+      </c>
+      <c r="N26" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="27">
@@ -15880,6 +16090,12 @@
           <t>NODE_S2016_17_0019</t>
         </is>
       </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0027</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
           <t>complete</t>
@@ -15889,6 +16105,14 @@
         <is>
           <t>NODE_S2015_16_0026</t>
         </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N27" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="28">
@@ -15922,6 +16146,8 @@
           <t>NODE_S2016_17_0019</t>
         </is>
       </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
           <t>complete</t>
@@ -15931,6 +16157,14 @@
         <is>
           <t>NODE_S2015_16_0027</t>
         </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N28" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="29">
@@ -15964,6 +16198,8 @@
           <t>NODE_S2016_17_0019</t>
         </is>
       </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
           <t>complete</t>
@@ -15973,6 +16209,14 @@
         <is>
           <t>NODE_S2015_16_0028</t>
         </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N29" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -16411,10 +16655,20 @@
           <t>NODE_S2016_17_0037</t>
         </is>
       </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>9 týmů</t>
+        </is>
+      </c>
+      <c r="N40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -16490,10 +16744,20 @@
           <t>NODE_S2016_17_0037</t>
         </is>
       </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (horní)</t>
+        </is>
+      </c>
+      <c r="N42" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="43">
@@ -16601,10 +16865,24 @@
           <t>NODE_S2016_17_0042</t>
         </is>
       </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0045</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>13 týmů</t>
+        </is>
+      </c>
+      <c r="N45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -16638,10 +16916,24 @@
           <t>NODE_S2016_17_0042</t>
         </is>
       </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0050</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>horní polovina ZČ</t>
+        </is>
+      </c>
+      <c r="N46" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="47">
@@ -16823,10 +17115,24 @@
           <t>NODE_S2016_17_0042</t>
         </is>
       </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0053</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N51" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="52">
@@ -16934,10 +17240,20 @@
           <t>NODE_S2016_17_0042</t>
         </is>
       </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N54" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="55">
@@ -17045,10 +17361,24 @@
           <t>NODE_S2016_17_0042</t>
         </is>
       </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0045</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
       <c r="J57" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>13 týmů</t>
+        </is>
+      </c>
+      <c r="N57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -17082,10 +17412,24 @@
           <t>NODE_S2016_17_0042</t>
         </is>
       </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0053</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
       <c r="J58" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N58" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="59">
@@ -17193,10 +17537,20 @@
           <t>NODE_S2016_17_0042</t>
         </is>
       </c>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N61" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="62">
@@ -17341,10 +17695,24 @@
           <t>NODE_S2016_17_0062</t>
         </is>
       </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0065</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr"/>
       <c r="J65" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>12 týmů</t>
+        </is>
+      </c>
+      <c r="N65" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -17378,10 +17746,24 @@
           <t>NODE_S2016_17_0062</t>
         </is>
       </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0070</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr"/>
       <c r="J66" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>horní polovina ZČ</t>
+        </is>
+      </c>
+      <c r="N66" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="67">
@@ -17563,10 +17945,24 @@
           <t>NODE_S2016_17_0062</t>
         </is>
       </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0073</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr"/>
       <c r="J71" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N71" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="72">
@@ -17674,10 +18070,20 @@
           <t>NODE_S2016_17_0062</t>
         </is>
       </c>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr"/>
       <c r="J74" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N74" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="75">
@@ -17822,10 +18228,24 @@
           <t>NODE_S2016_17_0075</t>
         </is>
       </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0079</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr"/>
       <c r="J78" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>8 týmů</t>
+        </is>
+      </c>
+      <c r="N78" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="79">
@@ -17901,10 +18321,24 @@
           <t>NODE_S2016_17_0075</t>
         </is>
       </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0082</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr"/>
       <c r="J80" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>horní polovina ZČ</t>
+        </is>
+      </c>
+      <c r="N80" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="81">
@@ -18012,10 +18446,24 @@
           <t>NODE_S2016_17_0075</t>
         </is>
       </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0085</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr"/>
       <c r="J83" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N83" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="84">
@@ -18123,10 +18571,20 @@
           <t>NODE_S2016_17_0075</t>
         </is>
       </c>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr"/>
       <c r="J86" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N86" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="87">
@@ -18271,10 +18729,24 @@
           <t>NODE_S2016_17_0075</t>
         </is>
       </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0082</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr"/>
       <c r="J90" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>horní polovina ZČ</t>
+        </is>
+      </c>
+      <c r="N90" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="91">
@@ -18456,10 +18928,24 @@
           <t>NODE_S2016_17_0075</t>
         </is>
       </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0085</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr"/>
       <c r="J95" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N95" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="96">
@@ -18567,10 +19053,20 @@
           <t>NODE_S2016_17_0075</t>
         </is>
       </c>
+      <c r="G98" t="inlineStr"/>
+      <c r="H98" t="inlineStr"/>
       <c r="J98" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N98" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="99">
@@ -18826,10 +19322,24 @@
           <t>NODE_S2016_17_0102</t>
         </is>
       </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0105</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr"/>
       <c r="J105" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>6 týmů</t>
+        </is>
+      </c>
+      <c r="N105" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="106">
@@ -18863,10 +19373,28 @@
           <t>NODE_S2016_17_0102</t>
         </is>
       </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0110</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0108</t>
+        </is>
+      </c>
       <c r="J106" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N106" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="107">
@@ -18974,10 +19502,20 @@
           <t>NODE_S2016_17_0102</t>
         </is>
       </c>
+      <c r="G109" t="inlineStr"/>
+      <c r="H109" t="inlineStr"/>
       <c r="J109" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>poražení SF</t>
+        </is>
+      </c>
+      <c r="N109" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="110">
@@ -19048,10 +19586,20 @@
           <t>NODE_S2016_17_0102</t>
         </is>
       </c>
+      <c r="G111" t="inlineStr"/>
+      <c r="H111" t="inlineStr"/>
       <c r="J111" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N111" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="112">
@@ -19159,10 +19707,24 @@
           <t>NODE_S2016_17_0102</t>
         </is>
       </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0105</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr"/>
       <c r="J114" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>6 týmů</t>
+        </is>
+      </c>
+      <c r="N114" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="115">
@@ -19196,10 +19758,28 @@
           <t>NODE_S2016_17_0102</t>
         </is>
       </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0110</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0108</t>
+        </is>
+      </c>
       <c r="J115" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N115" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="116">
@@ -19307,10 +19887,20 @@
           <t>NODE_S2016_17_0102</t>
         </is>
       </c>
+      <c r="G118" t="inlineStr"/>
+      <c r="H118" t="inlineStr"/>
       <c r="J118" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>poražení SF</t>
+        </is>
+      </c>
+      <c r="N118" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="119">
@@ -19381,10 +19971,20 @@
           <t>NODE_S2016_17_0102</t>
         </is>
       </c>
+      <c r="G120" t="inlineStr"/>
+      <c r="H120" t="inlineStr"/>
       <c r="J120" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N120" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="121">
@@ -19566,10 +20166,24 @@
           <t>NODE_S2016_17_0122</t>
         </is>
       </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0125</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr"/>
       <c r="J125" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>4 týmů</t>
+        </is>
+      </c>
+      <c r="N125" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="126">
@@ -19603,10 +20217,24 @@
           <t>NODE_S2016_17_0122</t>
         </is>
       </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0128</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr"/>
       <c r="J126" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N126" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="127">
@@ -19714,10 +20342,20 @@
           <t>NODE_S2016_17_0122</t>
         </is>
       </c>
+      <c r="G129" t="inlineStr"/>
+      <c r="H129" t="inlineStr"/>
       <c r="J129" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N129" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="130">
@@ -19862,10 +20500,24 @@
           <t>NODE_S2016_17_0130</t>
         </is>
       </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0135</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr"/>
       <c r="J133" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>7 týmů</t>
+        </is>
+      </c>
+      <c r="N133" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="134">
@@ -19936,10 +20588,20 @@
           <t>NODE_S2016_17_0130</t>
         </is>
       </c>
+      <c r="G135" t="inlineStr"/>
+      <c r="H135" t="inlineStr"/>
       <c r="J135" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (horní)</t>
+        </is>
+      </c>
+      <c r="N135" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="136">
@@ -19973,10 +20635,24 @@
           <t>NODE_S2016_17_0130</t>
         </is>
       </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0138</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr"/>
       <c r="J136" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>horní polovina ZČ</t>
+        </is>
+      </c>
+      <c r="N136" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="137">
@@ -20084,10 +20760,28 @@
           <t>NODE_S2016_17_0130</t>
         </is>
       </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0143</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0141</t>
+        </is>
+      </c>
       <c r="J139" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N139" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="140">
@@ -20195,10 +20889,20 @@
           <t>NODE_S2016_17_0130</t>
         </is>
       </c>
+      <c r="G142" t="inlineStr"/>
+      <c r="H142" t="inlineStr"/>
       <c r="J142" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>poražení SF</t>
+        </is>
+      </c>
+      <c r="N142" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="143">
@@ -20269,10 +20973,20 @@
           <t>NODE_S2016_17_0130</t>
         </is>
       </c>
+      <c r="G144" t="inlineStr"/>
+      <c r="H144" t="inlineStr"/>
       <c r="J144" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N144" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="145">
@@ -20454,10 +21168,24 @@
           <t>NODE_S2016_17_0146</t>
         </is>
       </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0149</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr"/>
       <c r="J149" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>8 týmů</t>
+        </is>
+      </c>
+      <c r="N149" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="150">
@@ -20491,10 +21219,24 @@
           <t>NODE_S2016_17_0146</t>
         </is>
       </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0152</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr"/>
       <c r="J150" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>horní polovina ZČ</t>
+        </is>
+      </c>
+      <c r="N150" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="151">
@@ -20602,10 +21344,28 @@
           <t>NODE_S2016_17_0146</t>
         </is>
       </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0157</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0155</t>
+        </is>
+      </c>
       <c r="J153" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N153" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="154">
@@ -20713,10 +21473,20 @@
           <t>NODE_S2016_17_0146</t>
         </is>
       </c>
+      <c r="G156" t="inlineStr"/>
+      <c r="H156" t="inlineStr"/>
       <c r="J156" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>poražení SF</t>
+        </is>
+      </c>
+      <c r="N156" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="157">
@@ -20787,10 +21557,20 @@
           <t>NODE_S2016_17_0146</t>
         </is>
       </c>
+      <c r="G158" t="inlineStr"/>
+      <c r="H158" t="inlineStr"/>
       <c r="J158" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N158" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="159">
@@ -20940,10 +21720,24 @@
           <t>NODE_S2016_17_0146</t>
         </is>
       </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0149</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr"/>
       <c r="J162" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>8 týmů</t>
+        </is>
+      </c>
+      <c r="N162" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="163">
@@ -21019,10 +21813,20 @@
           <t>NODE_S2016_17_0146</t>
         </is>
       </c>
+      <c r="G164" t="inlineStr"/>
+      <c r="H164" t="inlineStr"/>
       <c r="J164" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N164" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="165">
@@ -21167,10 +21971,24 @@
           <t>NODE_S2016_17_0165</t>
         </is>
       </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0172</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr"/>
       <c r="J168" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>11 týmů</t>
+        </is>
+      </c>
+      <c r="N168" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="169">
@@ -21241,10 +22059,20 @@
           <t>NODE_S2016_17_0165</t>
         </is>
       </c>
+      <c r="G170" t="inlineStr"/>
+      <c r="H170" t="inlineStr"/>
       <c r="J170" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (dolní)</t>
+        </is>
+      </c>
+      <c r="N170" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="171">
@@ -21357,10 +22185,24 @@
           <t>NODE_S2016_17_0165</t>
         </is>
       </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0183</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr"/>
       <c r="J173" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>střed tabulky ZČ</t>
+        </is>
+      </c>
+      <c r="N173" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="174">
@@ -21468,10 +22310,28 @@
           <t>NODE_S2016_17_0165</t>
         </is>
       </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0180</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0178</t>
+        </is>
+      </c>
       <c r="J176" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N176" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="177">
@@ -21579,10 +22439,20 @@
           <t>NODE_S2016_17_0165</t>
         </is>
       </c>
+      <c r="G179" t="inlineStr"/>
+      <c r="H179" t="inlineStr"/>
       <c r="J179" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>poražení SF</t>
+        </is>
+      </c>
+      <c r="N179" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="180">
@@ -21653,10 +22523,20 @@
           <t>NODE_S2016_17_0165</t>
         </is>
       </c>
+      <c r="G181" t="inlineStr"/>
+      <c r="H181" t="inlineStr"/>
       <c r="J181" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N181" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="182">
@@ -21764,10 +22644,24 @@
           <t>NODE_S2016_17_0165</t>
         </is>
       </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0175</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr"/>
       <c r="J184" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>horní ZČ + postupující z předkola</t>
+        </is>
+      </c>
+      <c r="N184" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="185">
@@ -21838,10 +22732,20 @@
           <t>NODE_S2016_17_0165</t>
         </is>
       </c>
+      <c r="G186" t="inlineStr"/>
+      <c r="H186" t="inlineStr"/>
       <c r="J186" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (horní)</t>
+        </is>
+      </c>
+      <c r="N186" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="187">
@@ -21949,10 +22853,28 @@
           <t>NODE_S2016_17_0165</t>
         </is>
       </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0180</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0178</t>
+        </is>
+      </c>
       <c r="J189" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M189" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N189" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="190">
@@ -22060,10 +22982,20 @@
           <t>NODE_S2016_17_0165</t>
         </is>
       </c>
+      <c r="G192" t="inlineStr"/>
+      <c r="H192" t="inlineStr"/>
       <c r="J192" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M192" t="inlineStr">
+        <is>
+          <t>poražení SF</t>
+        </is>
+      </c>
+      <c r="N192" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="193">
@@ -22134,10 +23066,20 @@
           <t>NODE_S2016_17_0165</t>
         </is>
       </c>
+      <c r="G194" t="inlineStr"/>
+      <c r="H194" t="inlineStr"/>
       <c r="J194" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N194" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="195">
@@ -22319,10 +23261,24 @@
           <t>NODE_S2016_17_0195</t>
         </is>
       </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0201</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr"/>
       <c r="J199" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>6 týmů</t>
+        </is>
+      </c>
+      <c r="N199" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="200">
@@ -22356,10 +23312,20 @@
           <t>NODE_S2016_17_0195</t>
         </is>
       </c>
+      <c r="G200" t="inlineStr"/>
+      <c r="H200" t="inlineStr"/>
       <c r="J200" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>poražení SF</t>
+        </is>
+      </c>
+      <c r="N200" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="201">
@@ -22430,10 +23396,20 @@
           <t>NODE_S2016_17_0195</t>
         </is>
       </c>
+      <c r="G202" t="inlineStr"/>
+      <c r="H202" t="inlineStr"/>
       <c r="J202" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N202" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="203">
@@ -22578,10 +23554,24 @@
           <t>NODE_S2016_17_0203</t>
         </is>
       </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0206</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr"/>
       <c r="J206" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>13 týmů</t>
+        </is>
+      </c>
+      <c r="N206" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="207">
@@ -22615,10 +23605,24 @@
           <t>NODE_S2016_17_0203</t>
         </is>
       </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0211</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr"/>
       <c r="J207" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>horní polovina ZČ</t>
+        </is>
+      </c>
+      <c r="N207" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="208">
@@ -22800,10 +23804,24 @@
           <t>NODE_S2016_17_0203</t>
         </is>
       </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0214</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr"/>
       <c r="J212" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N212" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="213">
@@ -22911,10 +23929,20 @@
           <t>NODE_S2016_17_0203</t>
         </is>
       </c>
+      <c r="G215" t="inlineStr"/>
+      <c r="H215" t="inlineStr"/>
       <c r="J215" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N215" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="216">
@@ -23059,10 +24087,24 @@
           <t>NODE_S2016_17_0216</t>
         </is>
       </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0219</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr"/>
       <c r="J219" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>8 týmů</t>
+        </is>
+      </c>
+      <c r="N219" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="220">
@@ -23096,10 +24138,24 @@
           <t>NODE_S2016_17_0216</t>
         </is>
       </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0224</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr"/>
       <c r="J220" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>horní polovina ZČ</t>
+        </is>
+      </c>
+      <c r="N220" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="221">
@@ -23281,10 +24337,24 @@
           <t>NODE_S2016_17_0216</t>
         </is>
       </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0227</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr"/>
       <c r="J225" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N225" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="226">
@@ -23392,10 +24462,20 @@
           <t>NODE_S2016_17_0216</t>
         </is>
       </c>
+      <c r="G228" t="inlineStr"/>
+      <c r="H228" t="inlineStr"/>
       <c r="J228" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N228" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="229">

--- a/data/S2016_17_FINAL.xlsx
+++ b/data/S2016_17_FINAL.xlsx
@@ -1119,7 +1119,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -15039,7 +15039,6 @@
           <t>NODE_S2016_17_0006</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>complete</t>
@@ -15150,8 +15149,6 @@
           <t>NODE_S2016_17_0003</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>complete</t>
@@ -15202,8 +15199,6 @@
           <t>NODE_S2016_17_0003</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>complete</t>
@@ -15254,8 +15249,6 @@
           <t>NODE_S2016_17_0001</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>complete</t>
@@ -15515,7 +15508,6 @@
           <t>NODE_S2016_17_0015</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>complete</t>
@@ -15571,7 +15563,6 @@
           <t>NODE_S2016_17_0016</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>complete</t>
@@ -15622,8 +15613,6 @@
           <t>NODE_S2016_17_0011</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>complete</t>
@@ -15674,8 +15663,6 @@
           <t>NODE_S2016_17_0011</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
           <t>complete</t>
@@ -15983,7 +15970,6 @@
           <t>NODE_S2016_17_0025</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
           <t>complete</t>
@@ -16039,7 +16025,6 @@
           <t>NODE_S2016_17_0026</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
           <t>complete</t>
@@ -16095,7 +16080,6 @@
           <t>NODE_S2016_17_0027</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
           <t>complete</t>
@@ -16146,8 +16130,6 @@
           <t>NODE_S2016_17_0019</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
           <t>complete</t>
@@ -16198,8 +16180,6 @@
           <t>NODE_S2016_17_0019</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
           <t>complete</t>
@@ -16655,8 +16635,6 @@
           <t>NODE_S2016_17_0037</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
           <t>complete</t>
@@ -16744,8 +16722,6 @@
           <t>NODE_S2016_17_0037</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
           <t>complete</t>
@@ -16870,7 +16846,6 @@
           <t>NODE_S2016_17_0045</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
           <t>complete</t>
@@ -16921,7 +16896,6 @@
           <t>NODE_S2016_17_0050</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
           <t>complete</t>
@@ -17120,7 +17094,6 @@
           <t>NODE_S2016_17_0053</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
           <t>complete</t>
@@ -17240,8 +17213,6 @@
           <t>NODE_S2016_17_0042</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
           <t>complete</t>
@@ -17366,7 +17337,6 @@
           <t>NODE_S2016_17_0045</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr"/>
       <c r="J57" t="inlineStr">
         <is>
           <t>complete</t>
@@ -17417,7 +17387,6 @@
           <t>NODE_S2016_17_0053</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr"/>
       <c r="J58" t="inlineStr">
         <is>
           <t>complete</t>
@@ -17537,8 +17506,6 @@
           <t>NODE_S2016_17_0042</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
           <t>complete</t>
@@ -17700,7 +17667,6 @@
           <t>NODE_S2016_17_0065</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr"/>
       <c r="J65" t="inlineStr">
         <is>
           <t>complete</t>
@@ -17751,7 +17717,6 @@
           <t>NODE_S2016_17_0070</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr"/>
       <c r="J66" t="inlineStr">
         <is>
           <t>complete</t>
@@ -17950,7 +17915,6 @@
           <t>NODE_S2016_17_0073</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr"/>
       <c r="J71" t="inlineStr">
         <is>
           <t>complete</t>
@@ -18070,8 +18034,6 @@
           <t>NODE_S2016_17_0062</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
       <c r="J74" t="inlineStr">
         <is>
           <t>complete</t>
@@ -18233,7 +18195,6 @@
           <t>NODE_S2016_17_0079</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr"/>
       <c r="J78" t="inlineStr">
         <is>
           <t>complete</t>
@@ -18326,7 +18287,6 @@
           <t>NODE_S2016_17_0082</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr"/>
       <c r="J80" t="inlineStr">
         <is>
           <t>complete</t>
@@ -18451,7 +18411,6 @@
           <t>NODE_S2016_17_0085</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr"/>
       <c r="J83" t="inlineStr">
         <is>
           <t>complete</t>
@@ -18571,8 +18530,6 @@
           <t>NODE_S2016_17_0075</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr"/>
-      <c r="H86" t="inlineStr"/>
       <c r="J86" t="inlineStr">
         <is>
           <t>complete</t>
@@ -18734,7 +18691,6 @@
           <t>NODE_S2016_17_0082</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr"/>
       <c r="J90" t="inlineStr">
         <is>
           <t>complete</t>
@@ -18933,7 +18889,6 @@
           <t>NODE_S2016_17_0085</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr"/>
       <c r="J95" t="inlineStr">
         <is>
           <t>complete</t>
@@ -19053,8 +19008,6 @@
           <t>NODE_S2016_17_0075</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr"/>
-      <c r="H98" t="inlineStr"/>
       <c r="J98" t="inlineStr">
         <is>
           <t>complete</t>
@@ -19327,7 +19280,6 @@
           <t>NODE_S2016_17_0105</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr"/>
       <c r="J105" t="inlineStr">
         <is>
           <t>complete</t>
@@ -19502,8 +19454,6 @@
           <t>NODE_S2016_17_0102</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr"/>
-      <c r="H109" t="inlineStr"/>
       <c r="J109" t="inlineStr">
         <is>
           <t>complete</t>
@@ -19586,8 +19536,6 @@
           <t>NODE_S2016_17_0102</t>
         </is>
       </c>
-      <c r="G111" t="inlineStr"/>
-      <c r="H111" t="inlineStr"/>
       <c r="J111" t="inlineStr">
         <is>
           <t>complete</t>
@@ -19712,7 +19660,6 @@
           <t>NODE_S2016_17_0105</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr"/>
       <c r="J114" t="inlineStr">
         <is>
           <t>complete</t>
@@ -19887,8 +19834,6 @@
           <t>NODE_S2016_17_0102</t>
         </is>
       </c>
-      <c r="G118" t="inlineStr"/>
-      <c r="H118" t="inlineStr"/>
       <c r="J118" t="inlineStr">
         <is>
           <t>complete</t>
@@ -19971,8 +19916,6 @@
           <t>NODE_S2016_17_0102</t>
         </is>
       </c>
-      <c r="G120" t="inlineStr"/>
-      <c r="H120" t="inlineStr"/>
       <c r="J120" t="inlineStr">
         <is>
           <t>complete</t>
@@ -20171,7 +20114,6 @@
           <t>NODE_S2016_17_0125</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr"/>
       <c r="J125" t="inlineStr">
         <is>
           <t>complete</t>
@@ -20222,7 +20164,6 @@
           <t>NODE_S2016_17_0128</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr"/>
       <c r="J126" t="inlineStr">
         <is>
           <t>complete</t>
@@ -20342,8 +20283,6 @@
           <t>NODE_S2016_17_0122</t>
         </is>
       </c>
-      <c r="G129" t="inlineStr"/>
-      <c r="H129" t="inlineStr"/>
       <c r="J129" t="inlineStr">
         <is>
           <t>complete</t>
@@ -20505,7 +20444,6 @@
           <t>NODE_S2016_17_0135</t>
         </is>
       </c>
-      <c r="H133" t="inlineStr"/>
       <c r="J133" t="inlineStr">
         <is>
           <t>complete</t>
@@ -20588,8 +20526,6 @@
           <t>NODE_S2016_17_0130</t>
         </is>
       </c>
-      <c r="G135" t="inlineStr"/>
-      <c r="H135" t="inlineStr"/>
       <c r="J135" t="inlineStr">
         <is>
           <t>complete</t>
@@ -20640,7 +20576,6 @@
           <t>NODE_S2016_17_0138</t>
         </is>
       </c>
-      <c r="H136" t="inlineStr"/>
       <c r="J136" t="inlineStr">
         <is>
           <t>complete</t>
@@ -20889,8 +20824,6 @@
           <t>NODE_S2016_17_0130</t>
         </is>
       </c>
-      <c r="G142" t="inlineStr"/>
-      <c r="H142" t="inlineStr"/>
       <c r="J142" t="inlineStr">
         <is>
           <t>complete</t>
@@ -20973,8 +20906,6 @@
           <t>NODE_S2016_17_0130</t>
         </is>
       </c>
-      <c r="G144" t="inlineStr"/>
-      <c r="H144" t="inlineStr"/>
       <c r="J144" t="inlineStr">
         <is>
           <t>complete</t>
@@ -21173,7 +21104,6 @@
           <t>NODE_S2016_17_0149</t>
         </is>
       </c>
-      <c r="H149" t="inlineStr"/>
       <c r="J149" t="inlineStr">
         <is>
           <t>complete</t>
@@ -21224,7 +21154,6 @@
           <t>NODE_S2016_17_0152</t>
         </is>
       </c>
-      <c r="H150" t="inlineStr"/>
       <c r="J150" t="inlineStr">
         <is>
           <t>complete</t>
@@ -21473,8 +21402,6 @@
           <t>NODE_S2016_17_0146</t>
         </is>
       </c>
-      <c r="G156" t="inlineStr"/>
-      <c r="H156" t="inlineStr"/>
       <c r="J156" t="inlineStr">
         <is>
           <t>complete</t>
@@ -21557,8 +21484,6 @@
           <t>NODE_S2016_17_0146</t>
         </is>
       </c>
-      <c r="G158" t="inlineStr"/>
-      <c r="H158" t="inlineStr"/>
       <c r="J158" t="inlineStr">
         <is>
           <t>complete</t>
@@ -21725,7 +21650,6 @@
           <t>NODE_S2016_17_0149</t>
         </is>
       </c>
-      <c r="H162" t="inlineStr"/>
       <c r="J162" t="inlineStr">
         <is>
           <t>complete</t>
@@ -21813,8 +21737,6 @@
           <t>NODE_S2016_17_0146</t>
         </is>
       </c>
-      <c r="G164" t="inlineStr"/>
-      <c r="H164" t="inlineStr"/>
       <c r="J164" t="inlineStr">
         <is>
           <t>complete</t>
@@ -21976,7 +21898,6 @@
           <t>NODE_S2016_17_0172</t>
         </is>
       </c>
-      <c r="H168" t="inlineStr"/>
       <c r="J168" t="inlineStr">
         <is>
           <t>complete</t>
@@ -22059,8 +21980,6 @@
           <t>NODE_S2016_17_0165</t>
         </is>
       </c>
-      <c r="G170" t="inlineStr"/>
-      <c r="H170" t="inlineStr"/>
       <c r="J170" t="inlineStr">
         <is>
           <t>complete</t>
@@ -22190,7 +22109,6 @@
           <t>NODE_S2016_17_0183</t>
         </is>
       </c>
-      <c r="H173" t="inlineStr"/>
       <c r="J173" t="inlineStr">
         <is>
           <t>complete</t>
@@ -22439,8 +22357,6 @@
           <t>NODE_S2016_17_0165</t>
         </is>
       </c>
-      <c r="G179" t="inlineStr"/>
-      <c r="H179" t="inlineStr"/>
       <c r="J179" t="inlineStr">
         <is>
           <t>complete</t>
@@ -22523,8 +22439,6 @@
           <t>NODE_S2016_17_0165</t>
         </is>
       </c>
-      <c r="G181" t="inlineStr"/>
-      <c r="H181" t="inlineStr"/>
       <c r="J181" t="inlineStr">
         <is>
           <t>complete</t>
@@ -22649,7 +22563,6 @@
           <t>NODE_S2016_17_0175</t>
         </is>
       </c>
-      <c r="H184" t="inlineStr"/>
       <c r="J184" t="inlineStr">
         <is>
           <t>complete</t>
@@ -22732,8 +22645,6 @@
           <t>NODE_S2016_17_0165</t>
         </is>
       </c>
-      <c r="G186" t="inlineStr"/>
-      <c r="H186" t="inlineStr"/>
       <c r="J186" t="inlineStr">
         <is>
           <t>complete</t>
@@ -22982,8 +22893,6 @@
           <t>NODE_S2016_17_0165</t>
         </is>
       </c>
-      <c r="G192" t="inlineStr"/>
-      <c r="H192" t="inlineStr"/>
       <c r="J192" t="inlineStr">
         <is>
           <t>complete</t>
@@ -23066,8 +22975,6 @@
           <t>NODE_S2016_17_0165</t>
         </is>
       </c>
-      <c r="G194" t="inlineStr"/>
-      <c r="H194" t="inlineStr"/>
       <c r="J194" t="inlineStr">
         <is>
           <t>complete</t>
@@ -23266,7 +23173,6 @@
           <t>NODE_S2016_17_0201</t>
         </is>
       </c>
-      <c r="H199" t="inlineStr"/>
       <c r="J199" t="inlineStr">
         <is>
           <t>complete</t>
@@ -23312,8 +23218,6 @@
           <t>NODE_S2016_17_0195</t>
         </is>
       </c>
-      <c r="G200" t="inlineStr"/>
-      <c r="H200" t="inlineStr"/>
       <c r="J200" t="inlineStr">
         <is>
           <t>complete</t>
@@ -23396,8 +23300,6 @@
           <t>NODE_S2016_17_0195</t>
         </is>
       </c>
-      <c r="G202" t="inlineStr"/>
-      <c r="H202" t="inlineStr"/>
       <c r="J202" t="inlineStr">
         <is>
           <t>complete</t>
@@ -23559,7 +23461,6 @@
           <t>NODE_S2016_17_0206</t>
         </is>
       </c>
-      <c r="H206" t="inlineStr"/>
       <c r="J206" t="inlineStr">
         <is>
           <t>complete</t>
@@ -23610,7 +23511,6 @@
           <t>NODE_S2016_17_0211</t>
         </is>
       </c>
-      <c r="H207" t="inlineStr"/>
       <c r="J207" t="inlineStr">
         <is>
           <t>complete</t>
@@ -23809,7 +23709,6 @@
           <t>NODE_S2016_17_0214</t>
         </is>
       </c>
-      <c r="H212" t="inlineStr"/>
       <c r="J212" t="inlineStr">
         <is>
           <t>complete</t>
@@ -23929,8 +23828,6 @@
           <t>NODE_S2016_17_0203</t>
         </is>
       </c>
-      <c r="G215" t="inlineStr"/>
-      <c r="H215" t="inlineStr"/>
       <c r="J215" t="inlineStr">
         <is>
           <t>complete</t>
@@ -24092,7 +23989,6 @@
           <t>NODE_S2016_17_0219</t>
         </is>
       </c>
-      <c r="H219" t="inlineStr"/>
       <c r="J219" t="inlineStr">
         <is>
           <t>complete</t>
@@ -24143,7 +24039,6 @@
           <t>NODE_S2016_17_0224</t>
         </is>
       </c>
-      <c r="H220" t="inlineStr"/>
       <c r="J220" t="inlineStr">
         <is>
           <t>complete</t>
@@ -24342,7 +24237,6 @@
           <t>NODE_S2016_17_0227</t>
         </is>
       </c>
-      <c r="H225" t="inlineStr"/>
       <c r="J225" t="inlineStr">
         <is>
           <t>complete</t>
@@ -24462,8 +24356,6 @@
           <t>NODE_S2016_17_0216</t>
         </is>
       </c>
-      <c r="G228" t="inlineStr"/>
-      <c r="H228" t="inlineStr"/>
       <c r="J228" t="inlineStr">
         <is>
           <t>complete</t>
@@ -43764,7 +43656,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43836,6 +43728,18 @@
       <c r="B6" t="inlineStr">
         <is>
           <t>3 oprav kvalifikačních levelů. Sloupec Q (level) aktualizován.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>mistr</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>HC Kometa Brno</t>
         </is>
       </c>
     </row>

--- a/data/S2016_17_FINAL.xlsx
+++ b/data/S2016_17_FINAL.xlsx
@@ -5329,7 +5329,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W41"/>
+  <dimension ref="A1:W44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -7796,6 +7796,118 @@
       <c r="V41" s="2" t="n"/>
       <c r="W41" s="2" t="n"/>
     </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0229</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>3</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>HC Skuteč</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0229</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>CLUB_S2016_17_0289</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>TR_S2016_17_00289</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>4</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>TJ Orli Lanškroun</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0229</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>CLUB_S2016_17_0290</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>TR_S2016_17_00290</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7807,7 +7919,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W55"/>
+  <dimension ref="A1:W67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -10904,6 +11016,500 @@
       <c r="V55" s="2" t="n"/>
       <c r="W55" s="2" t="n"/>
     </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0230</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>2</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>HC Světlá nad Sázavou</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0230</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>CLUB_S2016_17_0291</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>TR_S2016_17_00291</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>8</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>HC Chotěboř</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0230</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>CLUB_S2016_17_0292</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>TR_S2016_17_00292</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>10</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>HC Ledeč nad Sázavou</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0230</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>CLUB_S2016_17_0293</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>TR_S2016_17_00293</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0231</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>1</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>HC Litomyšl B</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0231</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>CLUB_S2016_17_0294</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>TR_S2016_17_00294</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>2</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Spartak Choceň B</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0231</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>CLUB_S2016_17_0295</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>TR_S2016_17_00295</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>3</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Slovan Moravská Třebová B</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0231</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>CLUB_S2016_17_0296</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>TR_S2016_17_00296</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>4</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>TJ Voděrady</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0231</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>CLUB_S2016_17_0297</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>TR_S2016_17_00297</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>5</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>IHC Česká Třebová</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0231</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>CLUB_S2016_17_0298</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>TR_S2016_17_00298</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>6</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>SK Žamberk</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0231</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>CLUB_S2016_17_0299</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>TR_S2016_17_00299</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>7</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>HC Dlouhoňovice</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0231</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>CLUB_S2016_17_0300</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>TR_S2016_17_00300</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10915,7 +11521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W14"/>
+  <dimension ref="A1:W33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -11776,6 +12382,812 @@
       <c r="U14" s="2" t="n"/>
       <c r="V14" s="2" t="n"/>
       <c r="W14" s="2" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0232</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>soutěž se nehrála</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0232</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>CLUB_S2016_17_0301</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>TR_S2016_17_00301</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>3</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>HC Zastávka</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0232</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>CLUB_S2016_17_0302</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>TR_S2016_17_00302</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>4</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>HC Veverská Bítýška</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0232</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>CLUB_S2016_17_0303</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>TR_S2016_17_00303</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Jihlava</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0233</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>HC Chvojkovice – Brod</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Jihlava</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0233</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>CLUB_S2016_17_0304</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>TR_S2016_17_00304</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>HAS Jihlava</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Jihlava</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0233</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>CLUB_S2016_17_0305</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>TR_S2016_17_00305</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>3</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>HC Rantířov</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Jihlava</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0233</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>CLUB_S2016_17_0306</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>TR_S2016_17_00306</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>4</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>HC Velký Beranov</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Jihlava</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0233</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>CLUB_S2016_17_0307</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>TR_S2016_17_00307</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>5</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>HC Kokodáci</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Jihlava</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0233</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>CLUB_S2016_17_0308</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>TR_S2016_17_00308</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>6</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>HC Amatero Luka nad Jihlavou</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Jihlava</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0233</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>CLUB_S2016_17_0309</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>TR_S2016_17_00309</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Hellfis Třebíč</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Jihlava</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0233</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>CLUB_S2016_17_0310</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>TR_S2016_17_00310</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>2</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Horní Heřmanice</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Jihlava</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0233</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>CLUB_S2016_17_0311</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>TR_S2016_17_00311</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>3</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Sokol Stařeč</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Jihlava</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0233</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>CLUB_S2016_17_0312</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>TR_S2016_17_00312</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>4</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Sokol Okříšky</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Jihlava</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0233</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>CLUB_S2016_17_0313</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>TR_S2016_17_00313</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Náměšť nad Oslavou</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Jihlava</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0233</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>CLUB_S2016_17_0314</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>TR_S2016_17_00314</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>2</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>HC Ducks</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Jihlava</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0233</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>CLUB_S2016_17_0315</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>TR_S2016_17_00315</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>3</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>DTJ Ivančice</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Jihlava</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0233</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>CLUB_S2016_17_0316</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>TR_S2016_17_00316</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>4</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>HC Naloučany</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Jihlava</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0233</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>CLUB_S2016_17_0317</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>TR_S2016_17_00317</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -14724,7 +16136,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N229"/>
+  <dimension ref="A1:N234"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24404,6 +25816,191 @@
       <c r="J229" t="inlineStr">
         <is>
           <t>complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0229</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Hradecký – Krajská liga</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>league</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>REG_HKK</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0146</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy).</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0230</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Pardubický – Krajská liga</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>league</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>REG_PAK</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0165</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy).</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0231</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Pardubický – Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>league</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>REG_PAK</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0165</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy).</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0232</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Vysočina – Krajská liga</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>league</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>REG_VYS</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0195</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy).</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0233</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Vysočina – Jihlava</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>league</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>REG_VYS</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0195</t>
+        </is>
+      </c>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy).</t>
         </is>
       </c>
     </row>
@@ -29916,7 +31513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J289"/>
+  <dimension ref="A1:J318"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="8" max="8"/>
@@ -43642,6 +45239,789 @@
       <c r="J289" t="inlineStr">
         <is>
           <t>Nový Jičín</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>CLUB_S2016_17_0289</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>HC Skuteč</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>HC Skuteč</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>30HRAD</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>CLUB_S2016_17_0290</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>TJ Orli Lanškroun</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>TJ Orli Lanškroun</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>30HRAD</t>
+        </is>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>CLUB_S2016_17_0291</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>HC Světlá nad Sázavou</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>HC Světlá nad Sázavou</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>CLUB_S2016_17_0292</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>HC Chotěboř</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>HC Chotěboř</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>CLUB_S2016_17_0293</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>HC Ledeč nad Sázavou</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>HC Ledeč nad Sázavou</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>CLUB_S2016_17_0294</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>HC Litomyšl B</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>HC Litomyšl B</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>CLUB_S2016_17_0295</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>Spartak Choceň B</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>Spartak Choceň B</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>CLUB_S2016_17_0296</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>Slovan Moravská Třebová B</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>Slovan Moravská Třebová B</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>CLUB_S2016_17_0297</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>TJ Voděrady</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>TJ Voděrady</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>CLUB_S2016_17_0298</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>IHC Česká Třebová</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>IHC Česká Třebová</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>CLUB_S2016_17_0299</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>SK Žamberk</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>SK Žamberk</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>CLUB_S2016_17_0300</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>HC Dlouhoňovice</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>HC Dlouhoňovice</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>CLUB_S2016_17_0301</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>soutěž se nehrála</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>soutěž se nehrála</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>CLUB_S2016_17_0302</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>HC Zastávka</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>HC Zastávka</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>CLUB_S2016_17_0303</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>HC Veverská Bítýška</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>HC Veverská Bítýška</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>CLUB_S2016_17_0304</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>HC Chvojkovice – Brod</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>HC Chvojkovice – Brod</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>CLUB_S2016_17_0305</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>HAS Jihlava</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>HAS Jihlava</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>CLUB_S2016_17_0306</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>HC Rantířov</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>HC Rantířov</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>CLUB_S2016_17_0307</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>HC Velký Beranov</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>HC Velký Beranov</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>CLUB_S2016_17_0308</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>HC Kokodáci</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>HC Kokodáci</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>CLUB_S2016_17_0309</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>HC Amatero Luka nad Jihlavou</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>HC Amatero Luka nad Jihlavou</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>CLUB_S2016_17_0310</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>Hellfis Třebíč</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>Hellfis Třebíč</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>CLUB_S2016_17_0311</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>Horní Heřmanice</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>Horní Heřmanice</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>CLUB_S2016_17_0312</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>Sokol Stařeč</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>Sokol Stařeč</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>CLUB_S2016_17_0313</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>Sokol Okříšky</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>Sokol Okříšky</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>CLUB_S2016_17_0314</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>Náměšť nad Oslavou</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>Náměšť nad Oslavou</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>CLUB_S2016_17_0315</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>HC Ducks</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>HC Ducks</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>CLUB_S2016_17_0316</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>DTJ Ivančice</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>DTJ Ivančice</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>CLUB_S2016_17_0317</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>HC Naloučany</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>HC Naloučany</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>L40</t>
         </is>
       </c>
     </row>

--- a/data/S2016_17_FINAL.xlsx
+++ b/data/S2016_17_FINAL.xlsx
@@ -41,7 +41,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -60,8 +60,12 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00B45309"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -83,6 +87,11 @@
         <fgColor rgb="00305496"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE0B2"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -96,7 +105,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -107,6 +116,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -46134,7 +46145,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -46191,11 +46202,63 @@
           <t>NODE_S2016_17_0031</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>top-level kvalifikace bez feeds_into: 'KVAL L35'</t>
         </is>
       </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>torzo</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>skupina o 5.místo (Praha) · NODE_S2016_17_0041</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>máme jen 2 týmy (Bohemians Praha, HC Olympik Praha), chybí zbytek týmů a tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>torzo</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Hradecký – Krajská liga (Královéhradecký kraj) · NODE_S2016_17_0229</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>máme jen 2 týmy (HC Skuteč, TJ Orli Lanškroun), chybí zbytek týmů a tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F2"/>

--- a/data/S2016_17_FINAL.xlsx
+++ b/data/S2016_17_FINAL.xlsx
@@ -105,7 +105,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -118,6 +118,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -16009,7 +16012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16073,6 +16076,40 @@
         </is>
       </c>
       <c r="D3" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0041</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>[TBD] torzo: máme jen 2 týmy (Bohemians Praha, HC Olympik Praha), chybí zbytek týmů a tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>NODE_S2016_17_0229</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>[TBD] torzo: máme jen 2 týmy (HC Skuteč, TJ Orli Lanškroun), chybí zbytek týmů a tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -46222,7 +46259,7 @@
           <t>skupina o 5.místo (Praha) · NODE_S2016_17_0041</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D3" s="8" t="inlineStr">
         <is>
           <t>máme jen 2 týmy (Bohemians Praha, HC Olympik Praha), chybí zbytek týmů a tabulka  [torzo-audit]</t>
         </is>
@@ -46248,7 +46285,7 @@
           <t>Hradecký – Krajská liga (Královéhradecký kraj) · NODE_S2016_17_0229</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>máme jen 2 týmy (HC Skuteč, TJ Orli Lanškroun), chybí zbytek týmů a tabulka  [torzo-audit]</t>
         </is>

--- a/data/S2016_17_FINAL.xlsx
+++ b/data/S2016_17_FINAL.xlsx
@@ -17993,7 +17993,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>30_Praha L40</t>
+          <t>Praha, 4. úroveň</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -18204,7 +18204,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>30_Středočeský L40</t>
+          <t>Středočeský, 4. úroveň</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -19025,7 +19025,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>30_Jihočeský L40</t>
+          <t>Jihočeský, 4. úroveň</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -19236,7 +19236,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Sokol Radomyšl – Lokomotiva Veselí nad Lužnicí  3:0, 2:3</t>
+          <t>Sokol Radomyšl – Lokomotiva Veselí nad Lužnicí 3:0, 2:3</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -19273,7 +19273,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Slavoj Žirovnice – HC Milevsko 2010  1:3, 1:4</t>
+          <t>Slavoj Žirovnice – HC Milevsko 2010 1:3, 1:4</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -19434,7 +19434,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>TJ Hluboká nad Vltavou  - HC Milevsko 2010  6:3, 1:3</t>
+          <t>TJ Hluboká nad Vltavou - HC Milevsko 2010 6:3, 1:3</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -19553,7 +19553,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>30_Plzeňský L40</t>
+          <t>Plzeňský, 4. úroveň</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -20210,7 +20210,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>HC Nýřany  - HC DTJ Klabava  4:10, 4:6</t>
+          <t>HC Nýřany - HC DTJ Klabava 4:10, 4:6</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -20247,7 +20247,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Buldoci Stříbro - HC Pubec Plzeň  4:4, 2:8</t>
+          <t>Buldoci Stříbro - HC Pubec Plzeň 4:4, 2:8</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -20284,7 +20284,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Sokol Horní Lukavice  - Sokol Malá Víska  3:2, 3:4, nájezdy 0:1</t>
+          <t>Sokol Horní Lukavice - Sokol Malá Víska 3:2, 3:4, nájezdy 0:1</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -20408,7 +20408,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>HC Pubec Plzeň  - HC DTJ Klabava  7:2, 4:3</t>
+          <t>HC Pubec Plzeň - HC DTJ Klabava 7:2, 4:3</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -20490,7 +20490,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Sokol Malá Víska - HC Pubec Plzeň  6:5, 7:2</t>
+          <t>Sokol Malá Víska - HC Pubec Plzeň 6:5, 7:2</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -20638,7 +20638,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>30_Karlovarský L40</t>
+          <t>Karlovarský, 4. úroveň</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -21197,7 +21197,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Stadion Cheb "B" – IHT Brimstones Cheb  8:4,5:2</t>
+          <t>Stadion Cheb "B" – IHT Brimstones Cheb 8:4,5:2</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -21472,7 +21472,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>30_Ústecký L40</t>
+          <t>Ústecký, 4. úroveň</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -21646,7 +21646,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Slovan Louny – HC Lovosice  5:4,8:1</t>
+          <t>Slovan Louny – HC Lovosice 5:4,8:1</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -21683,7 +21683,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>HC Roudnice nad Labem  - SK Kadaň "B" 3:4,3:4</t>
+          <t>HC Roudnice nad Labem - SK Kadaň "B" 3:4,3:4</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -21802,7 +21802,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>30_Liberecký L40</t>
+          <t>Liberecký, 4. úroveň</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -22058,7 +22058,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>HC Frýdlant – HC Turnov 1931  3:2 SN, 3:6, tie-break 1:0</t>
+          <t>HC Frýdlant – HC Turnov 1931 3:2 SN, 3:6, tie-break 1:0</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -22187,7 +22187,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Slavoj Liberec – HC Frýdlant  5:2,13:1</t>
+          <t>Slavoj Liberec – HC Frýdlant 5:2,13:1</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -22306,7 +22306,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>HC Děčín "B" – HC Frýdlant  6:3,4:3 PP</t>
+          <t>HC Děčín "B" – HC Frýdlant 6:3,4:3 PP</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -22462,7 +22462,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>30_Hradecký L40</t>
+          <t>Hradecký, 4. úroveň</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -22765,7 +22765,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>HC Rodos Dvůr Králové nad Labem – Wikow Hronov  4:8,6:3,8:1,11:1</t>
+          <t>HC Rodos Dvůr Králové nad Labem – Wikow Hronov 4:8,6:3,8:1,11:1</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -23219,7 +23219,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>TJ Orli Lanškroun – Sokol Semechnice  8:4,3:4,2:3 SN</t>
+          <t>TJ Orli Lanškroun – Sokol Semechnice 8:4,3:4,2:3 SN</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -23256,7 +23256,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>30_Pardubický L40</t>
+          <t>Pardubický, 4. úroveň</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -23591,7 +23591,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>BK Havlíčkův Brod "B" – HC Chotěboř  1:4,5:6</t>
+          <t>BK Havlíčkův Brod "B" – HC Chotěboř 1:4,5:6</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -23720,7 +23720,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Spartak Choceň – HC Chotěboř  7:1,1:7,2:7</t>
+          <t>Spartak Choceň – HC Chotěboř 7:1,1:7,2:7</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -23757,7 +23757,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>HC Hlinsko – HC Litomyšl  4:5,4:3 SN,5:1</t>
+          <t>HC Hlinsko – HC Litomyšl 4:5,4:3 SN,5:1</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -24127,7 +24127,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Spartak Choceň – HC Chrudim  3:11,4:5,3:4 PP</t>
+          <t>Spartak Choceň – HC Chrudim 3:11,4:5,3:4 PP</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -24164,7 +24164,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Kohouti Česká Třebová  - BK Havlíčkův Brod "B" 10:2,5:0,3:4 SN,2:5,4:3</t>
+          <t>Kohouti Česká Třebová - BK Havlíčkův Brod "B" 10:2,5:0,3:4 SN,2:5,4:3</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -24256,7 +24256,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Kohouti Česká Třebová  - HC Chrudim 5:3,3:6,4:3,3:2</t>
+          <t>Kohouti Česká Třebová - HC Chrudim 5:3,3:6,4:3,3:2</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -24494,7 +24494,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>30_Vysočina L40</t>
+          <t>Vysočina, 4. úroveň</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -24700,7 +24700,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>HC Zastávka - HC Veverská Bítýška  5:2,8:4</t>
+          <t>HC Zastávka - HC Veverská Bítýška 5:2,8:4</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -24782,7 +24782,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>BK Zubři Bystřice nad Pernštejnem  - TJ Náměšť nad Oslavou 3:4 SN,1:2 SN</t>
+          <t>BK Zubři Bystřice nad Pernštejnem - TJ Náměšť nad Oslavou 3:4 SN,1:2 SN</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -24819,7 +24819,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40</t>
+          <t>Jihomoravský, 4. úroveň</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -25310,7 +25310,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>HHK Velké Meziříčí – SKMB Boskovice   4:2,2:3,3:4 SN</t>
+          <t>HHK Velké Meziříčí – SKMB Boskovice 4:2,2:3,3:4 SN</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -25347,7 +25347,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>30_Severomoravský L40</t>
+          <t>Severomoravský, 4. úroveň</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -25521,7 +25521,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>HC Orli Orlová 1930 – HK Nový Jičín "B"  6:2,4:0</t>
+          <t>HC Orli Orlová 1930 – HK Nový Jičín "B" 6:2,4:0</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -25595,7 +25595,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>HC Studénka – Wolves Český Těšín  11:3,8:5</t>
+          <t>HC Studénka – Wolves Český Těšín 11:3,8:5</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -25632,7 +25632,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>TJ Horní Benešov – HK Krnov  2:5,4:5</t>
+          <t>TJ Horní Benešov – HK Krnov 2:5,4:5</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -25719,7 +25719,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>HC Orli Orlová 1930  - HK Krnov  5:4 PP,4:1</t>
+          <t>HC Orli Orlová 1930 - HK Krnov 5:4 PP,4:1</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -25756,7 +25756,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>HC Bospor Bohumín – HC Studénka  2:1 PP,3:0</t>
+          <t>HC Bospor Bohumín – HC Studénka 2:1 PP,3:0</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -25838,7 +25838,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>HC Orli Orlová 1930  - HC Bospor Bohumín 4:2,3:2</t>
+          <t>HC Orli Orlová 1930 - HC Bospor Bohumín 4:2,3:2</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">

--- a/data/S2016_17_FINAL.xlsx
+++ b/data/S2016_17_FINAL.xlsx
@@ -814,7 +814,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -1549,7 +1549,7 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -1622,7 +1622,7 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -3900,7 +3900,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -3973,7 +3973,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -4046,7 +4046,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -4124,7 +4124,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -4197,7 +4197,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -4343,7 +4343,7 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -5707,7 +5707,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -5780,7 +5780,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -5858,7 +5858,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -6004,7 +6004,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -6077,7 +6077,7 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -8224,7 +8224,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -8297,7 +8297,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -8370,7 +8370,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -8443,7 +8443,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -8516,7 +8516,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -8589,7 +8589,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -8667,7 +8667,7 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -8740,7 +8740,7 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -8813,7 +8813,7 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -8886,7 +8886,7 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -8959,7 +8959,7 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -26350,7 +26350,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>zanik</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -26423,7 +26423,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>zanik</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -26496,7 +26496,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>zanik</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -26569,7 +26569,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>zanik</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -26642,7 +26642,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>zanik</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -26715,7 +26715,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -26788,7 +26788,7 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -26861,7 +26861,7 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -26939,7 +26939,7 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -27012,7 +27012,7 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -27085,7 +27085,7 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -27158,7 +27158,7 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -27231,7 +27231,7 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -27304,7 +27304,7 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -49728,7 +49728,7 @@
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
@@ -49801,7 +49801,7 @@
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
@@ -49874,7 +49874,7 @@
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
@@ -53791,7 +53791,7 @@
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>setrval?</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
@@ -53864,7 +53864,7 @@
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>setrval?</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
@@ -53937,7 +53937,7 @@
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>setrval?</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
@@ -54015,7 +54015,7 @@
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>setrval?</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
@@ -54088,7 +54088,7 @@
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>setrval?</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
@@ -54161,7 +54161,7 @@
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>setrval?</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
@@ -54239,7 +54239,7 @@
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>setrval?</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
@@ -54312,7 +54312,7 @@
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>setrval?</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
@@ -54385,7 +54385,7 @@
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>setrval?</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
@@ -54458,7 +54458,7 @@
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>setrval?</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
@@ -54531,7 +54531,7 @@
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>setrval?</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
@@ -54604,7 +54604,7 @@
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>setrval?</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
@@ -54677,7 +54677,7 @@
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>setrval?</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
@@ -62346,7 +62346,7 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>setrval?</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -62424,7 +62424,7 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>setrval?</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -62497,7 +62497,7 @@
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>setrval?</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
@@ -62570,7 +62570,7 @@
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>setrval?</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -62643,7 +62643,7 @@
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>setrval?</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
@@ -62716,7 +62716,7 @@
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>setrval?</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
